--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -767,7 +767,7 @@
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -779,7 +779,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -794,25 +794,25 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">43
+</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -821,7 +821,7 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">468
 </t>
@@ -833,9 +833,9 @@
 </t>
         </is>
       </c>
-      <c r="W4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -847,13 +847,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
@@ -872,7 +872,9 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>08561435132</t>
+          <t xml:space="preserve">27
+2
+</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -883,7 +885,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -895,11 +897,15 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">84
@@ -926,13 +932,13 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -950,7 +956,7 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -962,7 +968,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -974,7 +980,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -998,14 +1004,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>808</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1023,12 +1028,14 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>08561435132</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">27
+2
+</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -1038,10 +1045,15 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -1059,7 +1071,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1069,33 +1081,32 @@
 </t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>4887</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1113,7 +1124,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1137,12 +1148,13 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1172,18 +1184,18 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>352</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1201,7 +1213,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1219,7 +1231,8 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -1236,13 +1249,13 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -1254,7 +1267,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -1296,13 +1309,13 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1327,36 +1340,32 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">344
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -1364,31 +1373,32 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">022
+</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">365
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1411,7 +1421,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1429,18 +1439,17 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1469,27 +1478,38 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660
-</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>611</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
+          <t xml:space="preserve">533
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n"/>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2262
+411464141
+</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">442
@@ -1504,26 +1524,26 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
@@ -1535,13 +1555,13 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">16850
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1554,7 +1574,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -1566,25 +1586,25 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1062
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -1603,17 +1623,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1642,39 +1664,35 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>326</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t xml:space="preserve">366
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">330
@@ -1689,48 +1707,48 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">448
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">382
+</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1841
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">448
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1502
 </t>
         </is>
       </c>
@@ -1749,13 +1767,13 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
+          <t xml:space="preserve">4229
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -1772,24 +1790,23 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>411</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K11" s="3" t="n"/>
@@ -1808,17 +1825,18 @@
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2
+8
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1837,13 +1855,13 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">2290
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1855,19 +1873,19 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="X11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">023
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">4240
 </t>
         </is>
       </c>
@@ -1887,19 +1905,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 6
-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 317
+          <t xml:space="preserve">567
+</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1911,13 +1929,14 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1934,7 +1953,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1952,7 +1971,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -1968,20 +1987,20 @@
 </t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1993,17 +2012,17 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">151
 </t>
@@ -2011,17 +2030,14 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>048</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="n"/>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">45
+76
 </t>
         </is>
       </c>
@@ -2040,7 +2056,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
@@ -2052,7 +2068,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2068,7 +2084,7 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
 </t>
@@ -2106,7 +2122,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -2118,7 +2134,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">396
 </t>
         </is>
       </c>
@@ -2128,9 +2144,9 @@
 </t>
         </is>
       </c>
-      <c r="R13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2148,20 +2164,19 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">496
+</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
@@ -2172,7 +2187,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
@@ -2204,7 +2219,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -2220,7 +2235,7 @@
 </t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">114
 </t>
@@ -2240,13 +2255,13 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">020
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2258,13 +2273,13 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -2274,13 +2289,13 @@
 </t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">803
-</t>
-        </is>
-      </c>
-      <c r="R14" s="8" t="inlineStr">
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">145
 </t>
@@ -2288,7 +2303,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2300,20 +2315,18 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -2350,19 +2363,18 @@
           <t>343</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">795
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">163
 </t>
@@ -2387,7 +2399,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2397,7 +2409,7 @@
 </t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">120
 </t>
@@ -2405,7 +2417,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2427,15 +2439,15 @@
 </t>
         </is>
       </c>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -2453,7 +2465,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -2477,7 +2489,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -2496,25 +2508,24 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95721
+          <t xml:space="preserve">25777
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11896
+          <t xml:space="preserve">526
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2531,49 +2542,56 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">353
+</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">1811
+14
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">8223
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
+          <t xml:space="preserve">443222
+181909191
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">21215
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
@@ -2590,11 +2608,17 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="n"/>
+          <t xml:space="preserve">8206
+</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+7918949
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1315
@@ -2603,7 +2627,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2615,13 +2639,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2640,25 +2664,25 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2670,77 +2694,77 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">425
 </t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">309
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">624
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
@@ -2748,28 +2772,30 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>963</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">7
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">449
 </t>
         </is>
       </c>
@@ -2788,50 +2814,47 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521
+          <t xml:space="preserve">521
+2
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>349</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 7
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">135
@@ -2840,30 +2863,30 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -2874,19 +2897,18 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">376
+          <t>1669</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
@@ -2916,7 +2938,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2935,17 +2957,23 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
+          <t xml:space="preserve">268
+2975
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n"/>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">229
@@ -2960,7 +2988,8 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -2976,7 +3005,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2991,15 +3020,10 @@
           <t>26</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
@@ -3011,10 +3035,11 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="R19" s="8" t="inlineStr">
+          <t xml:space="preserve">320
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
@@ -3034,30 +3059,29 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>962</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -3075,13 +3099,15 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5429
-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">446466240
+212
+79719019
+</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">123
@@ -3090,8 +3116,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3108,7 +3133,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3120,7 +3145,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3132,19 +3157,19 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -3156,13 +3181,13 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>106</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3179,23 +3204,27 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W20" s="8" t="inlineStr">
+          <t>72</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
         </is>
       </c>
-      <c r="X20" s="3" t="n"/>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">320
@@ -3218,14 +3247,19 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429
-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n"/>
+          <t xml:space="preserve">5422
+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3236,90 +3270,89 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
+</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4920
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -3337,7 +3370,8 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -3348,7 +3382,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>146</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3366,12 +3400,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>341</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3382,14 +3416,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3400,11 +3432,11 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -3412,7 +3444,8 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -3423,19 +3456,19 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3446,7 +3479,7 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -3463,7 +3496,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3475,7 +3508,8 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>982</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
@@ -3486,7 +3520,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3510,38 +3544,35 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25475
-</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">603
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t xml:space="preserve">868
+</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">44255
+82947
 </t>
         </is>
       </c>
@@ -3553,11 +3584,15 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n"/>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3565,35 +3600,35 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>736</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3604,19 +3639,18 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -3634,11 +3668,16 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1921
+</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3654,7 +3693,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>50261</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3665,30 +3704,31 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
-</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">784
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -3700,11 +3740,10 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
@@ -3712,34 +3751,33 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">546
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">544
-</t>
-        </is>
-      </c>
-      <c r="R24" s="8" t="inlineStr">
+          <t xml:space="preserve">83
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
@@ -3764,7 +3802,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3782,13 +3820,14 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3806,29 +3845,29 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">142
 </t>
@@ -3842,11 +3881,15 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="n"/>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3856,14 +3899,19 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
@@ -3875,13 +3923,13 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3893,18 +3941,21 @@
       <c r="T25" s="3" t="n"/>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t xml:space="preserve">21
+2
+</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6 11558
+          <t xml:space="preserve">182
+171111
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3916,8 +3967,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n"/>
@@ -3948,37 +3998,41 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">448
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">089
 </t>
         </is>
       </c>
@@ -3988,7 +4042,7 @@
 </t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
 </t>
@@ -3996,13 +4050,13 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
@@ -4026,7 +4080,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4036,30 +4090,32 @@
 </t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>28234</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">664
+</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">494
+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4079,17 +4135,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
@@ -4097,34 +4153,39 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">2858
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6816
-</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">104
 </t>
         </is>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">163
@@ -4139,19 +4200,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13220
+          <t xml:space="preserve">5280
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4169,7 +4230,7 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -4181,34 +4242,36 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>42</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>266</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">262
+309
 </t>
         </is>
       </c>
@@ -4233,7 +4296,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4242,9 +4305,9 @@
 </t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4256,17 +4319,17 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
 </t>
@@ -4274,7 +4337,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -4286,25 +4349,25 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">4280
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4314,7 +4377,7 @@
 </t>
         </is>
       </c>
-      <c r="R28" s="8" t="inlineStr">
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -4322,47 +4385,47 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>132</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">262
+309
 </t>
         </is>
       </c>
@@ -4381,20 +4444,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4411,12 +4471,13 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -4427,7 +4488,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4445,13 +4506,13 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4467,7 +4528,7 @@
 </t>
         </is>
       </c>
-      <c r="R29" s="8" t="inlineStr">
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
 </t>
@@ -4475,17 +4536,20 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">277
@@ -4526,13 +4590,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15616
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -4544,37 +4607,37 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4586,36 +4649,36 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>63</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2329
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -4626,12 +4689,13 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t xml:space="preserve">90
+</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11941
+          <t xml:space="preserve">1941
 </t>
         </is>
       </c>
@@ -4643,19 +4707,19 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -4675,8 +4739,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
-</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4687,11 +4750,11 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -4699,17 +4762,18 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t xml:space="preserve">50
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4721,7 +4785,7 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -4748,36 +4812,30 @@
 </t>
         </is>
       </c>
-      <c r="P31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Q31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">551
-</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">826
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">388
@@ -4804,7 +4862,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4827,12 +4885,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">338
@@ -4841,7 +4894,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -4853,36 +4906,31 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4917,44 +4965,45 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="n"/>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -4968,21 +5017,15 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">312
-</t>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>4444</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -5000,7 +5043,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -5011,13 +5054,13 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5029,24 +5072,25 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5056,25 +5100,25 @@
 </t>
         </is>
       </c>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="S33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">062
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">834
 </t>
@@ -5088,19 +5132,18 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z33" s="3" t="n"/>
@@ -5125,7 +5168,8 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>321</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -5154,7 +5198,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5172,12 +5216,13 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5201,18 +5246,19 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5242,19 +5288,20 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">116
+178
 </t>
         </is>
       </c>
@@ -5273,19 +5320,18 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4379
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">856
+          <t>501</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -5303,7 +5349,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5315,7 +5361,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5333,20 +5379,25 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5370,46 +5421,40 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5425,13 +5470,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -5447,7 +5492,7 @@
 </t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">133
 </t>
@@ -5467,60 +5512,54 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="inlineStr">
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">145
 </t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">340
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5532,13 +5571,13 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -5550,13 +5589,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
@@ -5573,57 +5612,50 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2222
-</t>
-        </is>
-      </c>
+      <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">8219
 </t>
         </is>
       </c>
@@ -5633,21 +5665,16 @@
 </t>
         </is>
       </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3898
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -5659,18 +5686,18 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
@@ -5687,22 +5714,26 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">790
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>492</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">962
+</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5721,9 +5752,9 @@
           <t>433</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
@@ -5735,7 +5766,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -5747,7 +5778,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5757,9 +5788,9 @@
 </t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3010
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -5777,12 +5808,13 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t xml:space="preserve">532
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
@@ -5794,19 +5826,19 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">335
+</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">485
 </t>
         </is>
       </c>
@@ -5818,37 +5850,38 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5872,22 +5905,21 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t>54444</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">821
 </t>
@@ -5895,42 +5927,48 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t>060004</t>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>406</t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -5960,13 +5998,13 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5976,10 +6014,9 @@
 </t>
         </is>
       </c>
-      <c r="W39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -5990,14 +6027,13 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3964
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6015,13 +6051,14 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -6044,14 +6081,13 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -6059,61 +6095,57 @@
           <t>22</t>
         </is>
       </c>
-      <c r="K40" s="8" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">510
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">610
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="R40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -6137,19 +6169,19 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -6168,13 +6200,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6185,31 +6217,31 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6221,90 +6253,90 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1975
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -6323,18 +6355,21 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">224
+4811
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>462</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6349,15 +6384,15 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">530
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6367,39 +6402,39 @@
 </t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6411,54 +6446,54 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>455</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -6477,20 +6512,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -6499,7 +6533,7 @@
 </t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
@@ -6507,31 +6541,30 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6543,35 +6576,32 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -6583,36 +6613,37 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="X43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2853
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6631,19 +6662,19 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -6653,9 +6684,9 @@
 </t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -6667,48 +6698,49 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">5815
+</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6718,15 +6750,15 @@
 </t>
         </is>
       </c>
-      <c r="R44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="S44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
@@ -6738,25 +6770,25 @@
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -6768,7 +6800,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6787,19 +6819,19 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
@@ -6817,19 +6849,19 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3560
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
@@ -6841,86 +6873,87 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8818
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>722</t>
+          <t xml:space="preserve">528
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>752</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1865
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">22
+11
 </t>
         </is>
       </c>
@@ -6939,25 +6972,25 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">2322
+</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">877
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1399
+          <t xml:space="preserve">2321
 </t>
         </is>
       </c>
@@ -6965,88 +6998,84 @@
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">609
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">622
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="R46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
@@ -7058,7 +7087,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">15698
 </t>
         </is>
       </c>
@@ -746,13 +746,8 @@
           <t>335</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -765,9 +760,9 @@
         </is>
       </c>
       <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
@@ -779,12 +774,16 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -798,20 +797,21 @@
 </t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">383
+</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -821,42 +821,12 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">468
-</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322
-</t>
-        </is>
-      </c>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -872,8 +842,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-2
+          <t xml:space="preserve">5127
 </t>
         </is>
       </c>
@@ -883,39 +852,38 @@
 </t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">217
 </t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -930,15 +898,15 @@
 </t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">355
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">655
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -950,17 +918,17 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">140
 </t>
@@ -968,49 +936,45 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">410
-</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">468
+</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>808</t>
+          <t xml:space="preserve">322
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1028,14 +992,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-2
+          <t xml:space="preserve">15048
 </t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -1045,22 +1008,21 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">223
 </t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206231
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1071,52 +1033,48 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
+          <t xml:space="preserve">11400
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">327
 </t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="R6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">152
 </t>
@@ -1124,48 +1082,49 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t xml:space="preserve">2012
+</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
@@ -1184,28 +1143,28 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
+          <t xml:space="preserve">5836
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+          <t>353</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">231
 </t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -1213,11 +1172,11 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">113
 </t>
@@ -1225,13 +1184,12 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
+          <t>461</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -1243,20 +1201,13 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1267,11 +1218,11 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
+          <t xml:space="preserve">347
+</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
@@ -1279,49 +1230,48 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
+          <t>44</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
@@ -1340,64 +1290,63 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
+          <t xml:space="preserve">4851
+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">344
+</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1510
+</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
-</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">2365
 </t>
         </is>
       </c>
@@ -1413,25 +1362,24 @@
 </t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="R8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">151
 </t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
+          <t>41</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">422
 </t>
@@ -1439,28 +1387,31 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
+          <t>451</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="X8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">867
+</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>342</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1478,133 +1429,134 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t xml:space="preserve">26360
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">11697
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">1164
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262
-411464141
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">16442
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">2587
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">11830
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">9497
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16850
+          <t xml:space="preserve">11690
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="n"/>
+          <t xml:space="preserve">718
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">12241
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">11397
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">1696
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">11862
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">11202
 </t>
         </is>
       </c>
@@ -1623,19 +1575,18 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -1645,7 +1596,7 @@
 </t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">232
 </t>
@@ -1653,102 +1604,109 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2366
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">88
 </t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">366
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">448
 </t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="W10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -1767,36 +1725,31 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4229
+          <t xml:space="preserve">14278
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1806,7 +1759,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K11" s="3" t="n"/>
@@ -1818,35 +1771,35 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t xml:space="preserve">1130
+</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">289
 </t>
         </is>
       </c>
-      <c r="R11" s="3" t="n"/>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1489
+</t>
+        </is>
+      </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">88
@@ -1855,40 +1808,25 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">217
 </t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4240
-</t>
-        </is>
-      </c>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1905,55 +1843,49 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">20 6 1
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
+          <t>448</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1965,42 +1897,42 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">313
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -2012,33 +1944,37 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="n"/>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">023
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470
+</t>
+        </is>
+      </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-76
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2056,23 +1992,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
+          <t xml:space="preserve">16013
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+          <t>343</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
@@ -2084,9 +2019,9 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -2096,7 +2031,7 @@
 </t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">157
 </t>
@@ -2104,7 +2039,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2116,29 +2051,24 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">12490
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">396
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">332
 </t>
@@ -2146,52 +2076,56 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">496
-</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872
+          <t>35</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">440
+</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12654
+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -2207,7 +2141,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
+          <t xml:space="preserve">14880
 </t>
         </is>
       </c>
@@ -2219,11 +2153,11 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -2235,9 +2169,9 @@
 </t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -2255,7 +2189,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -2265,81 +2199,69 @@
 </t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
+          <t xml:space="preserve">1490
+</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">303
 </t>
         </is>
       </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="n"/>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+          <t xml:space="preserve">0208
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4312
+</t>
+        </is>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -2355,7 +2277,8 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t xml:space="preserve">18329
+</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2365,16 +2288,17 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">795
-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+          <t xml:space="preserve">020
+</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">163
 </t>
@@ -2382,12 +2306,13 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2399,11 +2324,11 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">165
 </t>
@@ -2411,25 +2336,20 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -2439,36 +2359,21 @@
 </t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">380
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1154
+</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="n"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -2477,20 +2382,19 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2508,78 +2412,73 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25777
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">526
+          <t xml:space="preserve">12916
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t xml:space="preserve">27268
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>821</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">562
+</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-14
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8223
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">443222
-181909191
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">29529
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21215
+          <t xml:space="preserve">22120
 </t>
         </is>
       </c>
@@ -2591,13 +2490,14 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
+          <t xml:space="preserve">11547
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">10836
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2608,44 +2508,43 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8206
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-7918949
+          <t xml:space="preserve">11882
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1315
+          <t xml:space="preserve">11310
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">1483
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">112458
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">11244
 </t>
         </is>
       </c>
@@ -2664,109 +2563,102 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">3154
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">624
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">9425
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">723
+          <t>47</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">873
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
@@ -2778,27 +2670,23 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2292
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2814,48 +2702,57 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-2
+          <t xml:space="preserve">5321
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n"/>
+          <t xml:space="preserve">029
+</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="inlineStr">
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">135
 </t>
@@ -2863,82 +2760,74 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>59</t>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t xml:space="preserve">1155
+</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="n"/>
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -2957,20 +2846,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-2975
+          <t xml:space="preserve">3264
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">334
+</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -2988,48 +2876,45 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">135
 </t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">608
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3047,45 +2932,47 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">414
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="n"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">1
+</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -3099,18 +2986,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">446466240
-212
-79719019
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3119,7 +3004,7 @@
           <t>123</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">141
 </t>
@@ -3127,13 +3012,13 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -3145,11 +3030,10 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -3157,25 +3041,24 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
+          <t>73</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">5220
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3185,9 +3068,10 @@
 </t>
         </is>
       </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>106</t>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3204,34 +3088,40 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1824
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -3253,22 +3143,22 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">364
+</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">145
 </t>
@@ -3276,43 +3166,38 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">775
 </t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -3321,7 +3206,7 @@
           <t>420</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="P21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
@@ -3341,28 +3226,29 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
+          <t xml:space="preserve">366
+</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">263
 </t>
         </is>
       </c>
-      <c r="W21" s="3" t="inlineStr">
+      <c r="W21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">145
 </t>
@@ -3370,19 +3256,20 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3400,75 +3287,74 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t xml:space="preserve">15363
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2225
+</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">010
+</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">510
+</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3479,34 +3365,34 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">366
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
+          <t xml:space="preserve">1849
+</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">390
+</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
@@ -3520,17 +3406,22 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+          <t xml:space="preserve">2163
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3544,22 +3435,27 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2315
+</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">603
+          <t xml:space="preserve">1603
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">11171
 </t>
         </is>
       </c>
@@ -3571,8 +3467,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44255
-82947
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -3584,51 +3479,56 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">7191
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">12120
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">1412
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">1544
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>736</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3639,42 +3539,43 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">1829
+</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">1872
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">13026
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -3693,7 +3594,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>50261</t>
+          <t xml:space="preserve">3095
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3704,45 +3606,41 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">114
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -3751,25 +3649,20 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">546
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -3777,7 +3670,7 @@
           <t>209</t>
         </is>
       </c>
-      <c r="R24" s="3" t="inlineStr">
+      <c r="R24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
@@ -3790,19 +3683,19 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3814,19 +3707,19 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3845,53 +3738,57 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
-</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">4255
+</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
+          <t>432</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">842
+</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="inlineStr">
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -3899,63 +3796,56 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1400
+</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="n"/>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="n"/>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-2
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-171111
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -3967,10 +3857,16 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+          <t xml:space="preserve">14575
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11121
+</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -3996,14 +3892,15 @@
 </t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -4013,30 +3910,30 @@
 </t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">159
 </t>
@@ -4044,19 +3941,14 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4068,7 +3960,7 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -4080,46 +3972,46 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="V26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
-</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">494
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="n"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+          <t xml:space="preserve">2270
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1250
+</t>
+        </is>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -4135,58 +4027,53 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">5501
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2858
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">163
 </t>
@@ -4194,84 +4081,68 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">985
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
+          <t>48</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="n"/>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10266
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
 </t>
         </is>
       </c>
@@ -4290,24 +4161,25 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
+          <t xml:space="preserve">16210
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -4319,13 +4191,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4337,7 +4208,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4347,85 +4218,86 @@
 </t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4280
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">14280
+</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434
+</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
+</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1660
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
 </t>
         </is>
       </c>
@@ -4444,22 +4316,25 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">6249
+</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
+          <t xml:space="preserve">344
+</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -4471,24 +4346,25 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
@@ -4500,35 +4376,34 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1413
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">140
 </t>
@@ -4536,21 +4411,17 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>456</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="n"/>
+      <c r="V29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">277
 </t>
@@ -4564,7 +4435,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -4574,7 +4445,12 @@
 </t>
         </is>
       </c>
-      <c r="Z29" s="3" t="n"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30682
+</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -4590,54 +4466,55 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">27819
+</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1570
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">3720
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">1558
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
@@ -4649,53 +4526,50 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t xml:space="preserve">1306
+</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
+          <t xml:space="preserve">2223
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t xml:space="preserve">709
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
+          <t xml:space="preserve">81941
 </t>
         </is>
       </c>
@@ -4707,22 +4581,17 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="n"/>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -4739,7 +4608,8 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t xml:space="preserve">2364
+</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4750,62 +4620,48 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">506
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">465
@@ -4814,41 +4670,42 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t xml:space="preserve">310
+</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="n"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="n"/>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
+      </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">388
 </t>
         </is>
       </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr">
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -4856,13 +4713,13 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
@@ -4885,7 +4742,12 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0111
+</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">338
@@ -4894,52 +4756,56 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="n"/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12321
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">390
@@ -4952,41 +4818,28 @@
 </t>
         </is>
       </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
+      <c r="Q32" s="3" t="n"/>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="n"/>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">137
 </t>
@@ -4994,16 +4847,17 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="n"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319
+</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -5017,25 +4871,31 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>4444</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4487
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">167
 </t>
@@ -5043,110 +4903,103 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">187
 </t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">336
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
+          <t xml:space="preserve">1410
+</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="n"/>
+      <c r="R33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
         </is>
       </c>
-      <c r="S33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062
-</t>
-        </is>
-      </c>
+      <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">834
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="n"/>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2180
+</t>
+        </is>
+      </c>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="X33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -5168,37 +5021,27 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -5210,7 +5053,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -5220,37 +5063,37 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">129522
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -5258,50 +5101,49 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">0250
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="W34" s="3" t="inlineStr">
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">127
 </t>
         </is>
       </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
+      <c r="X34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
-178
 </t>
         </is>
       </c>
@@ -5326,48 +5168,44 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -5379,37 +5217,32 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="n"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5421,19 +5254,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -5451,10 +5284,15 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+          <t xml:space="preserve">18398
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>4221</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5470,88 +5308,80 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">3413
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">211
+</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1940
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">145
 </t>
@@ -5559,46 +5389,51 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="inlineStr">
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="W36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">136
 </t>
         </is>
       </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
+      <c r="X36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5612,98 +5447,114 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>9661</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">11816
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">1689
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">11102
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">216
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="n"/>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8219
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">1232
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">12402
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">17826
+</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1478
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">341
+          <t xml:space="preserve">11410
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">11342
+</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5714,23 +5565,24 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t xml:space="preserve">9498
+</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t xml:space="preserve">1812
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -5749,138 +5601,125 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">4433
+</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">361
-</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">14180
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
@@ -5905,35 +5744,37 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>54444</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>3035</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">3146
+</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5944,43 +5785,39 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>406</t>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="n"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -5998,28 +5835,24 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
+          <t xml:space="preserve">1224
+</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="n"/>
+      <c r="W39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="X39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">114
 </t>
@@ -6027,13 +5860,14 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">3964
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t xml:space="preserve">2266
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6051,137 +5885,137 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">6171
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262217
+</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">086
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>948</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">342
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">942
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="n"/>
+      <c r="W40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">847
+</t>
+        </is>
+      </c>
+      <c r="X40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">81206
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">12216
 </t>
         </is>
       </c>
@@ -6200,144 +6034,139 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">5875
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
+          <t>3401</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6355,145 +6184,137 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-4811
+          <t xml:space="preserve">4811
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n"/>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9209
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="R42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">020
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6512,88 +6333,84 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">3540
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">305
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">312
-</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">041
+</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">197
+</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n"/>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="inlineStr">
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="n"/>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
@@ -6601,49 +6418,49 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">2013
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="X43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2853
+          <t xml:space="preserve">19253
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">2461
 </t>
         </is>
       </c>
@@ -6662,133 +6479,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">605
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">2380
+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
+</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">561
+</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">909
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="n"/>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5815
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="S44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="R44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1093
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="W44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="X44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6800,7 +6606,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1824
 </t>
         </is>
       </c>
@@ -6819,141 +6625,139 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">331029
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">118715
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
+          <t xml:space="preserve">1919
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">822246
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">15123
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">18222
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1110111
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18159
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">112265
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="n"/>
+          <t xml:space="preserve">10218
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1838
+</t>
+        </is>
+      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">18369
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">88886
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">214621
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1061
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">10987
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">12228
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-11
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
@@ -6972,122 +6776,123 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2322
-</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">877
-</t>
+          <t xml:space="preserve">5518
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>996</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321
-</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>5242</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>3321</t>
-        </is>
-      </c>
-      <c r="R46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n"/>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t>7519</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">908
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="n"/>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">648
-</t>
-        </is>
-      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,17 +737,23 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15698
+          <t xml:space="preserve">5628
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="8" t="inlineStr">
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -759,10 +765,15 @@
 </t>
         </is>
       </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">728
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -774,20 +785,31 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="n"/>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">345
 </t>
         </is>
       </c>
@@ -797,9 +819,9 @@
 </t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">383
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
@@ -811,7 +833,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -842,7 +864,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
+          <t xml:space="preserve">151 27 1
 </t>
         </is>
       </c>
@@ -852,61 +874,63 @@
 </t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">217
 </t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">764
+</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>442</t>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">655
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -918,7 +942,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -930,7 +954,7 @@
       </c>
       <c r="R5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -940,40 +964,44 @@
 </t>
         </is>
       </c>
-      <c r="T5" s="3" t="n"/>
-      <c r="U5" s="8" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>04449</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">468
 </t>
         </is>
       </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">284
 </t>
         </is>
       </c>
-      <c r="W5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
@@ -992,13 +1020,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15048
-</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">23048
+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
@@ -1014,15 +1042,16 @@
 </t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206231
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">75
+</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1039,7 +1068,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1051,30 +1080,35 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11400
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="8" t="inlineStr">
+          <t xml:space="preserve">21098
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">327
 </t>
         </is>
       </c>
-      <c r="R6" s="8" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">152
 </t>
@@ -1094,7 +1128,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -1104,9 +1138,9 @@
 </t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -1118,13 +1152,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -1149,7 +1183,8 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>353</t>
+          <t xml:space="preserve">353
+</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1158,13 +1193,13 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">231
 </t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -1184,12 +1219,13 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1201,13 +1237,20 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">350
+</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1218,11 +1261,11 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
-</t>
-        </is>
-      </c>
-      <c r="R7" s="8" t="inlineStr">
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
@@ -1230,49 +1273,49 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="W7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1290,63 +1333,74 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
+          <t xml:space="preserve">112851
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
+          <t xml:space="preserve">828
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">812
+</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2365
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
@@ -1368,26 +1422,28 @@
 </t>
         </is>
       </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">422
 </t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>451</t>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">019
+</t>
         </is>
       </c>
       <c r="W8" s="8" t="inlineStr">
@@ -1396,24 +1452,19 @@
 </t>
         </is>
       </c>
-      <c r="X8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">110982
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1429,13 +1480,13 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26360
+          <t xml:space="preserve">26660
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11697
+          <t xml:space="preserve">1697
 </t>
         </is>
       </c>
@@ -1445,7 +1496,12 @@
 </t>
         </is>
       </c>
-      <c r="F9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14134
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1454,55 +1510,61 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">3291
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16442
+          <t xml:space="preserve">6142
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">671
+</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">329
+</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2587
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9497
+          <t xml:space="preserve">487
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11690
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
@@ -1514,7 +1576,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -1532,7 +1594,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -1556,7 +1618,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11202
+          <t xml:space="preserve">11584
 </t>
         </is>
       </c>
@@ -1581,12 +1643,13 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
@@ -1596,7 +1659,7 @@
 </t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">232
 </t>
@@ -1604,13 +1667,13 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1621,7 +1684,7 @@
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -1629,25 +1692,20 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1659,12 +1717,13 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1676,37 +1735,37 @@
       </c>
       <c r="U10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
+          <t xml:space="preserve">948
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">279
 </t>
         </is>
       </c>
-      <c r="W10" s="8" t="inlineStr">
+      <c r="W10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">139
 </t>
         </is>
       </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+      <c r="X10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1725,44 +1784,58 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14278
-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n"/>
+          <t xml:space="preserve">4279
+</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>06</t>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -1771,7 +1844,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
@@ -1788,7 +1861,7 @@
 </t>
         </is>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">289
 </t>
@@ -1796,34 +1869,29 @@
       </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1489
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">8220
 </t>
         </is>
       </c>
       <c r="U11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="n"/>
       <c r="W11" s="3" t="n"/>
       <c r="X11" s="3" t="n"/>
       <c r="Y11" s="3" t="n"/>
@@ -1843,24 +1911,24 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 6 1
+          <t xml:space="preserve">2067
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1870,22 +1938,27 @@
 </t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="I12" s="3" t="n"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1903,28 +1976,29 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t xml:space="preserve">530
+</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="Q12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
@@ -1932,7 +2006,7 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1950,7 +2024,7 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1962,19 +2036,20 @@
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">023
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">12170
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">18358
+</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -1992,30 +2067,31 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16013
+          <t xml:space="preserve">6013
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">343
+</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+          <t xml:space="preserve">594
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -2031,7 +2107,7 @@
 </t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">157
 </t>
@@ -2039,7 +2115,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2058,40 +2134,41 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">332
 </t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">440
 </t>
@@ -2103,7 +2180,7 @@
 </t>
         </is>
       </c>
-      <c r="W13" s="3" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">151
 </t>
@@ -2111,19 +2188,19 @@
       </c>
       <c r="X13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">021
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">088
+</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12654
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2141,7 +2218,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14880
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
@@ -2153,112 +2230,133 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1490
-</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">303
 </t>
         </is>
       </c>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">360
 </t>
         </is>
       </c>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0208
+          <t xml:space="preserve">0808
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -2277,30 +2375,29 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18329
+          <t xml:space="preserve">2521
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">020
-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
+          <t xml:space="preserve">315
+</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>933</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2312,7 +2409,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -2324,43 +2421,58 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">165
 </t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">104
 </t>
         </is>
       </c>
-      <c r="N15" s="3" t="n"/>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1154
@@ -2369,12 +2481,16 @@
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="inlineStr">
+          <t xml:space="preserve">8208
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">140
 </t>
@@ -2386,17 +2502,8 @@
 </t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1234
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
+      <c r="Y15" s="3" t="n"/>
+      <c r="Z15" s="3" t="n"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -2412,36 +2519,37 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">2371
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12916
+          <t xml:space="preserve">1823916
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27268
+          <t xml:space="preserve">2168
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">1182
+</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
@@ -2459,23 +2567,28 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29529
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
+          <t xml:space="preserve">2028
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">22120
@@ -2490,13 +2603,13 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11547
+          <t xml:space="preserve">1547
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10836
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
@@ -2514,37 +2627,37 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11882
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11310
+          <t xml:space="preserve">1315
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1483
+          <t xml:space="preserve">483
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112458
+          <t xml:space="preserve">11438
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11244
+          <t xml:space="preserve">10244
 </t>
         </is>
       </c>
@@ -2567,31 +2680,31 @@
 </t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">2316
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
@@ -2610,7 +2723,7 @@
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -2618,13 +2731,19 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9425
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2642,30 +2761,31 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
@@ -2682,11 +2802,16 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2292
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2702,25 +2827,24 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5321
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">029
-</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
+          <t xml:space="preserve">10321
+</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
@@ -2732,18 +2856,18 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2752,7 +2876,7 @@
 </t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">135
 </t>
@@ -2764,7 +2888,12 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="3" t="n"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -2773,18 +2902,19 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t>9111</t>
-        </is>
-      </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">804
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2796,26 +2926,31 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
+          <t xml:space="preserve">1185
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">404
 </t>
         </is>
       </c>
-      <c r="V18" s="3" t="n"/>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">081
+</t>
+        </is>
+      </c>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2827,7 +2962,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2846,20 +2981,18 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
+          <t xml:space="preserve">354
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -2888,7 +3021,7 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -2898,23 +3031,33 @@
 </t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2924,7 +3067,7 @@
 </t>
         </is>
       </c>
-      <c r="R19" s="3" t="inlineStr">
+      <c r="R19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
@@ -2938,17 +3081,22 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="n"/>
+          <t xml:space="preserve">614
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">129
@@ -2957,7 +3105,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -2969,7 +3117,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2988,12 +3136,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="8" t="inlineStr">
+          <t xml:space="preserve">93905
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
 </t>
@@ -3001,16 +3154,17 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">141
 </t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">149
 </t>
@@ -3024,16 +3178,16 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -3041,24 +3195,25 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -3068,7 +3223,7 @@
 </t>
         </is>
       </c>
-      <c r="R20" s="8" t="inlineStr">
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">146
 </t>
@@ -3094,31 +3249,31 @@
       </c>
       <c r="V20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">6202
 </t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1824
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -3137,41 +3292,47 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5422
+          <t xml:space="preserve">9422
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">145
 </t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
@@ -3179,13 +3340,13 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">775
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3195,18 +3356,19 @@
 </t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
@@ -3226,13 +3388,13 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3244,19 +3406,19 @@
       </c>
       <c r="V21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">863
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3268,7 +3430,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2176
 </t>
         </is>
       </c>
@@ -3287,13 +3449,14 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15363
+          <t xml:space="preserve">5363
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3304,17 +3467,17 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225
-</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
@@ -3332,25 +3495,30 @@
 </t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">010
-</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">107
 </t>
         </is>
       </c>
-      <c r="N22" s="3" t="n"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">510
@@ -3365,7 +3533,8 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">313
+</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -3376,17 +3545,17 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
-</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">390
 </t>
@@ -3398,7 +3567,7 @@
 </t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr">
+      <c r="W22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">146
 </t>
@@ -3412,13 +3581,13 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3437,13 +3606,13 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2315
+          <t xml:space="preserve">25175
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
@@ -3455,19 +3624,18 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11171
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">1868
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
@@ -3491,55 +3659,55 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7191
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">503
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12120
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
+          <t xml:space="preserve">566
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
@@ -3551,7 +3719,7 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13026
+          <t xml:space="preserve">1388
 </t>
         </is>
       </c>
@@ -3563,7 +3731,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
@@ -3575,7 +3743,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">11274
 </t>
         </is>
       </c>
@@ -3594,91 +3762,103 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3095
-</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">046
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">346
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">147
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">046
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="R24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -3699,27 +3879,22 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
+      <c r="W24" s="3" t="n"/>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3738,19 +3913,20 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4255
-</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">4555
+</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -3761,11 +3937,11 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
-</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
@@ -3773,7 +3949,8 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">61
+</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3788,59 +3965,68 @@
 </t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
+          <t xml:space="preserve">400
 </t>
         </is>
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">040
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="n"/>
+          <t xml:space="preserve">1480
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">873
+</t>
+        </is>
+      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
+          <t xml:space="preserve">428
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>77</t>
         </is>
       </c>
       <c r="W25" s="8" t="inlineStr">
@@ -3857,13 +4043,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14575
+          <t xml:space="preserve">14114
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11121
+          <t xml:space="preserve">218218280
 </t>
         </is>
       </c>
@@ -3882,7 +4068,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
+          <t xml:space="preserve">2304
 </t>
         </is>
       </c>
@@ -3892,33 +4078,34 @@
 </t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055
 </t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3929,26 +4116,31 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">105
 </t>
         </is>
       </c>
-      <c r="N26" s="3" t="n"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">8120
 </t>
         </is>
       </c>
@@ -3958,13 +4150,13 @@
 </t>
         </is>
       </c>
-      <c r="Q26" s="3" t="inlineStr">
+      <c r="Q26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">293
 </t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
+      <c r="R26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">142
 </t>
@@ -3972,7 +4164,8 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -3987,7 +4180,7 @@
 </t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
+      <c r="V26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
@@ -3995,21 +4188,25 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4033,10 +4230,11 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
+          <t xml:space="preserve">31 18
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">152
 </t>
@@ -4044,13 +4242,13 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -4060,22 +4258,27 @@
 </t>
         </is>
       </c>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
@@ -4085,7 +4288,12 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="3" t="n"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
@@ -4106,43 +4314,50 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="n"/>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1160
 </t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">374
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="n"/>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="n"/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">18659
 </t>
         </is>
       </c>
@@ -4161,143 +4376,144 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16210
-</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
+          <t xml:space="preserve">352
+</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04646
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1420
+</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">681
+</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
+</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14280
-</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1208
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">434
-</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277
-</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
@@ -4316,7 +4532,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
+          <t xml:space="preserve">6248
 </t>
         </is>
       </c>
@@ -4328,13 +4544,13 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -4346,25 +4562,24 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">008
+          <t>497</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4376,18 +4591,19 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -4397,9 +4613,9 @@
 </t>
         </is>
       </c>
-      <c r="Q29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">835
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4411,7 +4627,8 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>456</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -4420,10 +4637,15 @@
 </t>
         </is>
       </c>
-      <c r="U29" s="3" t="n"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">421
+</t>
+        </is>
+      </c>
       <c r="V29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">757
 </t>
         </is>
       </c>
@@ -4441,13 +4663,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30682
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4466,7 +4688,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
+          <t xml:space="preserve">21819
 </t>
         </is>
       </c>
@@ -4478,7 +4700,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
+          <t xml:space="preserve">7265
 </t>
         </is>
       </c>
@@ -4490,7 +4712,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
@@ -4502,19 +4724,19 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1558
+          <t xml:space="preserve">1398
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -4526,13 +4748,13 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1306
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4550,7 +4772,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1591
 </t>
         </is>
       </c>
@@ -4560,16 +4782,21 @@
 </t>
         </is>
       </c>
-      <c r="S30" s="3" t="n"/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">318
+</t>
+        </is>
+      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81941
+          <t xml:space="preserve">11941
 </t>
         </is>
       </c>
@@ -4587,12 +4814,21 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" s="3" t="n"/>
+          <t xml:space="preserve">11900
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4608,7 +4844,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">8564
 </t>
         </is>
       </c>
@@ -4620,7 +4856,8 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>489</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4631,8 +4868,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4653,15 +4889,30 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">015
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110 1
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">465
@@ -4680,16 +4931,20 @@
 </t>
         </is>
       </c>
-      <c r="R31" s="8" t="inlineStr">
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">142
 </t>
         </is>
       </c>
-      <c r="S31" s="3" t="n"/>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4699,13 +4954,13 @@
 </t>
         </is>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -4713,13 +4968,13 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -4744,13 +4999,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0111
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">338
+          <t>61444</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
@@ -4760,26 +5014,28 @@
 </t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
 </t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12321
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">621
+</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">942
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -4790,22 +5046,28 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n"/>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">390
@@ -4814,32 +5076,47 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336
+</t>
+        </is>
+      </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">141
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="n"/>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="U32" s="3" t="n"/>
-      <c r="V32" s="8" t="inlineStr">
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">283
 </t>
         </is>
       </c>
-      <c r="W32" s="8" t="inlineStr">
+      <c r="W32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">137
 </t>
@@ -4851,10 +5128,15 @@
 </t>
         </is>
       </c>
-      <c r="Y32" s="3" t="n"/>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">349
 </t>
         </is>
       </c>
@@ -4873,19 +5155,19 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487
+          <t xml:space="preserve">6137
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">312
+</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4921,11 +5203,11 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">187
 </t>
@@ -4939,46 +5221,56 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410
-</t>
-        </is>
-      </c>
-      <c r="P33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
         </is>
       </c>
-      <c r="S33" s="3" t="n"/>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="n"/>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">834
+</t>
+        </is>
+      </c>
       <c r="V33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">617
 </t>
         </is>
       </c>
@@ -4990,13 +5282,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">14554
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1039
 </t>
         </is>
       </c>
@@ -5015,8 +5307,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
+          <t>38463</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -5025,23 +5316,33 @@
 </t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">056
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">232
 </t>
         </is>
       </c>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5057,33 +5358,33 @@
 </t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">172
 </t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">114
 </t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129522
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5095,35 +5396,35 @@
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="V34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W34" s="8" t="inlineStr">
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">127
 </t>
@@ -5137,13 +5438,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">18606
 </t>
         </is>
       </c>
@@ -5162,87 +5463,97 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
+          <t xml:space="preserve">4399
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">503
+</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">303
 </t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1240
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -5254,17 +5565,17 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">235
 </t>
@@ -5278,19 +5589,20 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18398
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5318,60 +5630,70 @@
 </t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="M36" s="8" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">123
 </t>
         </is>
       </c>
-      <c r="N36" s="3" t="n"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5381,7 +5703,7 @@
 </t>
         </is>
       </c>
-      <c r="R36" s="8" t="inlineStr">
+      <c r="R36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">145
 </t>
@@ -5389,24 +5711,25 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8221
 </t>
         </is>
       </c>
@@ -5416,7 +5739,7 @@
 </t>
         </is>
       </c>
-      <c r="X36" s="8" t="inlineStr">
+      <c r="X36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
@@ -5424,13 +5747,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">14988
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5449,12 +5772,13 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t xml:space="preserve">22166
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11816
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -5466,7 +5790,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11102
+          <t xml:space="preserve">110253
 </t>
         </is>
       </c>
@@ -5478,7 +5802,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5490,30 +5814,32 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">10180
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>364</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">017
+</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -5524,65 +5850,67 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t xml:space="preserve">5935
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">1336
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17826
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11410
+          <t xml:space="preserve">1516
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11342
+          <t xml:space="preserve">1340
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">870
+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9498
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">13150
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -5601,101 +5929,115 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
+          <t xml:space="preserve">4733
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">681
+</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1112
-</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="n"/>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14180
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5744,35 +6086,35 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3146
+          <t xml:space="preserve">9146
 </t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">14126
 </t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">2119
 </t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+          <t xml:space="preserve">02101
+</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
@@ -5780,79 +6122,95 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>512</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5101
+</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2110
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="R39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">593
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1102
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="n"/>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1224
 </t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="n"/>
-      <c r="W39" s="8" t="inlineStr">
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="X39" s="8" t="inlineStr">
+      <c r="X39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">114
 </t>
@@ -5860,13 +6218,13 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3964
+          <t xml:space="preserve">964
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -5885,23 +6243,24 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">917
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">262217
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -5911,27 +6270,27 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">086
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -5949,7 +6308,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
@@ -5971,7 +6330,7 @@
 </t>
         </is>
       </c>
-      <c r="R40" s="8" t="inlineStr">
+      <c r="R40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
@@ -5979,12 +6338,13 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -5994,7 +6354,12 @@
 </t>
         </is>
       </c>
-      <c r="V40" s="3" t="n"/>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="W40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">847
@@ -6003,19 +6368,19 @@
       </c>
       <c r="X40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81206
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12216
+          <t xml:space="preserve">2216 3
 </t>
         </is>
       </c>
@@ -6040,12 +6405,12 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
@@ -6055,9 +6420,9 @@
 </t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16621
 </t>
         </is>
       </c>
@@ -6081,7 +6446,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
@@ -6091,13 +6456,18 @@
 </t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
+      <c r="M41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">119
 </t>
         </is>
       </c>
-      <c r="N41" s="3" t="n"/>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">490
@@ -6106,7 +6476,7 @@
       </c>
       <c r="P41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -6116,9 +6486,9 @@
 </t>
         </is>
       </c>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -6130,17 +6500,17 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">275
 </t>
@@ -6152,23 +6522,19 @@
 </t>
         </is>
       </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
+      <c r="X41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18284
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="n"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6188,30 +6554,31 @@
 </t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>3131</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">120
 </t>
@@ -6219,18 +6586,19 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -6246,10 +6614,15 @@
 </t>
         </is>
       </c>
-      <c r="N42" s="3" t="n"/>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9209
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
@@ -6261,10 +6634,11 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="R42" s="8" t="inlineStr">
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
@@ -6272,17 +6646,17 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -6296,28 +6670,23 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6333,13 +6702,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">2540
+</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">056
 </t>
         </is>
       </c>
@@ -6349,9 +6718,9 @@
 </t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -6369,18 +6738,19 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6390,21 +6760,31 @@
 </t>
         </is>
       </c>
-      <c r="M43" s="3" t="n"/>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n"/>
-      <c r="Q43" s="8" t="inlineStr">
+          <t xml:space="preserve">9216
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">289
 </t>
@@ -6418,31 +6798,31 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6454,13 +6834,13 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2461
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6479,7 +6859,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
@@ -6497,7 +6877,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">2229
 </t>
         </is>
       </c>
@@ -6507,21 +6887,31 @@
 </t>
         </is>
       </c>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">561
-</t>
-        </is>
-      </c>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">909
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="n"/>
-      <c r="L44" s="8" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
@@ -6529,7 +6919,8 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -6546,11 +6937,11 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="8" t="inlineStr">
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">292
 </t>
@@ -6564,19 +6955,19 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1093
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6594,7 +6985,7 @@
       </c>
       <c r="X44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6606,7 +6997,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1824
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
@@ -6623,144 +7014,140 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">331029
-</t>
-        </is>
-      </c>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118715
+          <t xml:space="preserve">15551
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">4119
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11221
+          <t xml:space="preserve">11021
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822246
+          <t xml:space="preserve">3450
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15123
+          <t xml:space="preserve">2263
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18222
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110111
+          <t xml:space="preserve">12919
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18159
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="n"/>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112265
+          <t xml:space="preserve">1022615
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">9204
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t xml:space="preserve">1284
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10218
+          <t xml:space="preserve">0118
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18369
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88886
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214621
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1061
+          <t xml:space="preserve">01010
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10987
+          <t xml:space="preserve">18 8
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12228
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11172
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12224
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6776,13 +7163,13 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>996</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6793,17 +7180,17 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">121
 </t>
@@ -6811,7 +7198,8 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -6821,7 +7209,7 @@
         </is>
       </c>
       <c r="K46" s="3" t="n"/>
-      <c r="L46" s="8" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -6829,14 +7217,19 @@
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="n"/>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -6846,7 +7239,7 @@
 </t>
         </is>
       </c>
-      <c r="Q46" s="8" t="inlineStr">
+      <c r="Q46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">288
 </t>
@@ -6854,7 +7247,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -6866,27 +7259,37 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,19 +737,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5628
+          <t xml:space="preserve">5698
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">937
 </t>
         </is>
       </c>
@@ -767,7 +767,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -797,13 +797,13 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -821,11 +821,11 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
-        </is>
-      </c>
-      <c r="R4" s="8" t="inlineStr">
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">137
 </t>
@@ -864,8 +864,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151 27 1
-</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -874,9 +873,9 @@
 </t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -888,13 +887,13 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">764
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -904,7 +903,7 @@
 </t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">129
 </t>
@@ -912,13 +911,13 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -930,7 +929,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -966,12 +965,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>04449</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -995,13 +995,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23048
+          <t xml:space="preserve">3068
 </t>
         </is>
       </c>
@@ -1036,15 +1036,15 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">223
 </t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -1056,79 +1056,79 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1008
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">85
 </t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">327
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21098
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">327
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -1138,10 +1138,9 @@
 </t>
         </is>
       </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">642
-</t>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
@@ -1152,13 +1151,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -1207,11 +1206,11 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">113
 </t>
@@ -1225,7 +1224,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1237,13 +1236,13 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1261,31 +1260,30 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1297,14 +1295,12 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1315,7 +1311,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1333,7 +1329,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112851
+          <t xml:space="preserve">2851
 </t>
         </is>
       </c>
@@ -1349,9 +1345,9 @@
 </t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1369,7 +1365,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -1379,15 +1375,15 @@
 </t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1400,7 +1396,7 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">32620
 </t>
         </is>
       </c>
@@ -1424,7 +1420,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -1440,13 +1436,13 @@
 </t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">019
-</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">153
 </t>
@@ -1454,13 +1450,13 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110982
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -1480,28 +1476,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26660
-</t>
+          <t>196565</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">11697
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14134
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">383
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1510,25 +1500,25 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3291
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -1540,7 +1530,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -1558,7 +1548,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
@@ -1618,7 +1608,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11584
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
@@ -1637,25 +1627,25 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">5312
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1667,8 +1657,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1705,7 +1694,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1723,7 +1712,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -1733,9 +1722,9 @@
 </t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">948
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -1751,7 +1740,7 @@
 </t>
         </is>
       </c>
-      <c r="X10" s="8" t="inlineStr">
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">878
 </t>
@@ -1759,7 +1748,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -1788,10 +1777,9 @@
 </t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1802,17 +1790,17 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
@@ -1820,7 +1808,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -1832,7 +1820,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1844,11 +1832,16 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n"/>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1130
@@ -1867,27 +1860,27 @@
 </t>
         </is>
       </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8220
-</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1917,117 +1910,112 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n"/>
       <c r="F12" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">0217
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">530
+</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">217
 </t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">530
-</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">892
-</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
       <c r="W12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">840
@@ -2036,19 +2024,19 @@
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">623
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12170
+          <t xml:space="preserve">14170
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18358
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2077,9 +2065,9 @@
 </t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">594
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -2089,22 +2077,16 @@
 </t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2134,7 +2116,7 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">8490
 </t>
         </is>
       </c>
@@ -2152,7 +2134,7 @@
       </c>
       <c r="R13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -2180,27 +2162,26 @@
 </t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
+      <c r="W13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">151
 </t>
         </is>
       </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">021
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2230,7 +2211,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2240,9 +2221,9 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2266,7 +2247,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2276,7 +2257,7 @@
 </t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">120
 </t>
@@ -2284,7 +2265,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2308,55 +2289,55 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">045
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">145
 </t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">360
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808
+          <t xml:space="preserve">10208
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
@@ -2375,29 +2356,28 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
+          <t xml:space="preserve">26521
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>731</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -2431,7 +2411,7 @@
 </t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">104
 </t>
@@ -2445,7 +2425,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
@@ -2455,50 +2435,44 @@
 </t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8208
-</t>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>981</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2519,25 +2493,25 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2371
+          <t xml:space="preserve">2572
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823916
+          <t xml:space="preserve">82916
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2168
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">11182
 </t>
         </is>
       </c>
@@ -2567,31 +2541,26 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1898
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22120
+          <t xml:space="preserve">22125
 </t>
         </is>
       </c>
@@ -2603,7 +2572,7 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
+          <t xml:space="preserve">1847
 </t>
         </is>
       </c>
@@ -2621,25 +2590,25 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1315
+          <t xml:space="preserve">1313
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -2651,7 +2620,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11438
+          <t xml:space="preserve">1458
 </t>
         </is>
       </c>
@@ -2676,31 +2645,30 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
-</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">23134
+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2316
+          <t>244</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2722,14 +2690,19 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">104
 </t>
@@ -2743,7 +2716,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
@@ -2767,7 +2740,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -2779,7 +2752,7 @@
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -2808,7 +2781,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2827,7 +2800,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10321
+          <t xml:space="preserve">2321
 </t>
         </is>
       </c>
@@ -2839,7 +2812,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -2848,26 +2821,21 @@
 </t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
+      <c r="G18" s="3" t="n"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2890,7 +2858,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2908,13 +2876,13 @@
       </c>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -2926,7 +2894,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -2938,7 +2906,7 @@
       </c>
       <c r="V18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -2950,19 +2918,19 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">2928
 </t>
         </is>
       </c>
@@ -2981,18 +2949,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3013,15 +2982,10 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1206
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -3033,8 +2997,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -3045,7 +3008,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -3075,7 +3038,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -3085,16 +3048,15 @@
 </t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">614
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3111,13 +3073,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">2928
 </t>
         </is>
       </c>
@@ -3136,26 +3098,23 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93905
-</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3164,7 +3123,7 @@
 </t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">149
 </t>
@@ -3178,7 +3137,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -3187,7 +3146,7 @@
 </t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -3199,15 +3158,15 @@
 </t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -3237,8 +3196,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -3247,13 +3205,13 @@
 </t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6202
-</t>
-        </is>
-      </c>
-      <c r="W20" s="8" t="inlineStr">
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
@@ -3261,13 +3219,13 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3292,25 +3250,25 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422
+          <t xml:space="preserve">0422
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">864
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -3328,7 +3286,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -3340,13 +3298,13 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">757
 </t>
         </is>
       </c>
@@ -3412,7 +3370,7 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -3424,13 +3382,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3449,7 +3407,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
+          <t xml:space="preserve">9363
 </t>
         </is>
       </c>
@@ -3465,9 +3423,9 @@
 </t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -3515,7 +3473,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -3551,11 +3509,11 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
+          <t xml:space="preserve">1849
+</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">390
 </t>
@@ -3567,15 +3525,15 @@
 </t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -3612,30 +3570,31 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">1603
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">11171
+</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -3659,7 +3618,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -3671,37 +3630,37 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
+          <t xml:space="preserve">12720
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
+          <t xml:space="preserve">2544
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">3686
 </t>
         </is>
       </c>
@@ -3719,13 +3678,13 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
+          <t xml:space="preserve">1386
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
+          <t xml:space="preserve">688
 </t>
         </is>
       </c>
@@ -3743,7 +3702,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11274
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -3762,12 +3721,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -3777,7 +3736,7 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">234
 </t>
@@ -3791,7 +3750,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
@@ -3801,18 +3760,13 @@
 </t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -3821,19 +3775,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3845,7 +3799,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3863,7 +3817,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3879,7 +3833,11 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="3" t="n"/>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">86
@@ -3888,13 +3846,13 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3931,7 +3889,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">0248
 </t>
         </is>
       </c>
@@ -3973,42 +3931,43 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">4010
 </t>
         </is>
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">040
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1480
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">373
 </t>
         </is>
       </c>
@@ -4020,16 +3979,16 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
+          <t>37</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
@@ -4043,13 +4002,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14114
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218218280
+          <t xml:space="preserve">11121
 </t>
         </is>
       </c>
@@ -4068,7 +4026,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">5304
 </t>
         </is>
       </c>
@@ -4090,9 +4048,9 @@
 </t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">055
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
@@ -4140,7 +4098,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8120
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -4150,13 +4108,12 @@
 </t>
         </is>
       </c>
-      <c r="Q26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="R26" s="8" t="inlineStr">
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">142
 </t>
@@ -4170,7 +4127,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -4182,11 +4139,11 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
@@ -4200,13 +4157,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">0220
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4224,13 +4181,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
+          <t xml:space="preserve">501
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 18
+          <t xml:space="preserve">318 4
 </t>
         </is>
       </c>
@@ -4242,13 +4199,13 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -4266,7 +4223,7 @@
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -4276,9 +4233,9 @@
 </t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">679
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4290,19 +4247,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -4326,23 +4283,27 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="n"/>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">96
@@ -4351,13 +4312,12 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18659
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
@@ -4376,36 +4336,37 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t xml:space="preserve">16210
+</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">352
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">04646
-</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
+          <t xml:space="preserve">376
+</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">816
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -4447,20 +4408,19 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="P28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
@@ -4471,19 +4431,19 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434
 </t>
         </is>
       </c>
@@ -4493,7 +4453,7 @@
 </t>
         </is>
       </c>
-      <c r="W28" s="8" t="inlineStr">
+      <c r="W28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">133
 </t>
@@ -4511,12 +4471,7 @@
 </t>
         </is>
       </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
-      </c>
+      <c r="Z28" s="3" t="n"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -4542,15 +4497,15 @@
 </t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -4568,18 +4523,18 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
+          <t>493</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
@@ -4603,19 +4558,19 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
@@ -4639,13 +4594,13 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
-</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">757
+          <t xml:space="preserve">471
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4657,19 +4612,19 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">230090
 </t>
         </is>
       </c>
@@ -4688,19 +4643,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21819
+          <t xml:space="preserve">22819
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">15616
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7265
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
@@ -4712,13 +4667,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1570
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4730,7 +4685,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4766,20 +4721,19 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1591
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -4790,13 +4744,13 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11941
+          <t xml:space="preserve">1941
 </t>
         </is>
       </c>
@@ -4814,19 +4768,19 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11900
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1069
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4844,7 +4798,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8564
+          <t xml:space="preserve">2364
 </t>
         </is>
       </c>
@@ -4868,7 +4822,8 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4883,7 +4838,7 @@
 </t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
@@ -4891,7 +4846,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -4939,7 +4894,8 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4999,13 +4955,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>61444</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">008
-</t>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>238</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5022,19 +4977,19 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5046,19 +5001,19 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5076,7 +5031,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5086,7 +5041,7 @@
 </t>
         </is>
       </c>
-      <c r="R32" s="8" t="inlineStr">
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">141
 </t>
@@ -5110,7 +5065,7 @@
 </t>
         </is>
       </c>
-      <c r="V32" s="3" t="inlineStr">
+      <c r="V32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">283
 </t>
@@ -5124,7 +5079,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -5136,7 +5091,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">349
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -5155,7 +5110,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6137
+          <t xml:space="preserve">1225
 </t>
         </is>
       </c>
@@ -5167,7 +5122,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -5177,7 +5132,7 @@
 </t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">167
 </t>
@@ -5191,7 +5146,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5203,7 +5158,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -5227,18 +5182,23 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n"/>
+          <t xml:space="preserve">410
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="R33" s="8" t="inlineStr">
+      <c r="R33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
@@ -5252,25 +5212,25 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
-</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
+          <t xml:space="preserve">934
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
         </is>
       </c>
-      <c r="W33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">617
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5282,14 +5242,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14554
+          <t xml:space="preserve">1492
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5307,7 +5266,8 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t xml:space="preserve">3866
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -5330,121 +5290,121 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">018
 </t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="R34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">324
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="X34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18606
+          <t xml:space="preserve">180 16
 </t>
         </is>
       </c>
@@ -5473,13 +5433,13 @@
 </t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">237
 </t>
@@ -5491,7 +5451,7 @@
 </t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">149
 </t>
@@ -5505,11 +5465,11 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K35" s="8" t="inlineStr">
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">143
 </t>
@@ -5529,7 +5489,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5541,17 +5501,12 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="R35" s="8" t="inlineStr">
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="n"/>
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">159
 </t>
@@ -5569,9 +5524,9 @@
 </t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -5595,16 +5550,11 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21215
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5639,11 +5589,11 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
@@ -5651,22 +5601,11 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -5681,13 +5620,13 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5717,7 +5656,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5727,9 +5666,9 @@
 </t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8221
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -5747,13 +5686,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14988
+          <t xml:space="preserve">11860
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -5778,7 +5717,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">118106
 </t>
         </is>
       </c>
@@ -5790,7 +5729,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110253
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
@@ -5802,7 +5741,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">338
 </t>
         </is>
       </c>
@@ -5814,31 +5753,31 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">032
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -5850,31 +5789,31 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1336
+          <t xml:space="preserve">133 5
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
+          <t xml:space="preserve">1478
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
@@ -5886,13 +5825,13 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
@@ -5904,13 +5843,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13150
+          <t xml:space="preserve">11812
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5929,11 +5868,11 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733
-</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
+          <t xml:space="preserve">4422
+</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">303
 </t>
@@ -5951,15 +5890,15 @@
 </t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">681
-</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -5977,7 +5916,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -5987,7 +5926,7 @@
 </t>
         </is>
       </c>
-      <c r="M38" s="8" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
@@ -5995,23 +5934,23 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">267
 </t>
@@ -6025,7 +5964,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -6037,7 +5976,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -6090,27 +6029,26 @@
 </t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1921
-</t>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>794</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">14126
+          <t xml:space="preserve">416
 </t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">1866
 </t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">02101
+          <t xml:space="preserve">08110
 </t>
         </is>
       </c>
@@ -6122,13 +6060,13 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -6140,11 +6078,11 @@
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5101
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">102
 </t>
@@ -6152,13 +6090,12 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6168,15 +6105,15 @@
 </t>
         </is>
       </c>
-      <c r="Q39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="R39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">593
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -6188,17 +6125,17 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">294
 </t>
         </is>
       </c>
-      <c r="V39" s="8" t="inlineStr">
+      <c r="V39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -6210,7 +6147,7 @@
 </t>
         </is>
       </c>
-      <c r="X39" s="3" t="inlineStr">
+      <c r="X39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">114
 </t>
@@ -6218,7 +6155,7 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">964
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
@@ -6243,12 +6180,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>64716</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">907
 </t>
         </is>
       </c>
@@ -6258,7 +6195,7 @@
 </t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">227
 </t>
@@ -6270,7 +6207,7 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
@@ -6278,7 +6215,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6290,7 +6227,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -6308,7 +6245,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6330,7 +6267,7 @@
 </t>
         </is>
       </c>
-      <c r="R40" s="3" t="inlineStr">
+      <c r="R40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
@@ -6348,9 +6285,9 @@
 </t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">942
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
@@ -6360,28 +6297,27 @@
 </t>
         </is>
       </c>
-      <c r="W40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="X40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216 3
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6405,12 +6341,13 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3141</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">314
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6420,21 +6357,21 @@
 </t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16621
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6446,7 +6383,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6470,13 +6407,13 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -6500,13 +6437,13 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -6518,7 +6455,7 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -6528,13 +6465,12 @@
 </t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18284
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="n"/>
+      <c r="Y41" s="3" t="n"/>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6554,31 +6490,31 @@
 </t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">120
 </t>
@@ -6586,7 +6522,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6602,7 +6538,7 @@
 </t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
+      <c r="L42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -6616,13 +6552,13 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -6634,7 +6570,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -6646,13 +6582,13 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6668,21 +6604,21 @@
 </t>
         </is>
       </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+      <c r="W42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6702,13 +6638,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2540
-</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">056
+          <t xml:space="preserve">5340
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -6732,7 +6668,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
@@ -6760,7 +6696,7 @@
 </t>
         </is>
       </c>
-      <c r="M43" s="8" t="inlineStr">
+      <c r="M43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">119
 </t>
@@ -6768,13 +6704,13 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9216
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -6790,7 +6726,7 @@
 </t>
         </is>
       </c>
-      <c r="R43" s="8" t="inlineStr">
+      <c r="R43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
@@ -6810,7 +6746,7 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -6822,7 +6758,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -6840,7 +6776,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -6869,15 +6805,15 @@
 </t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2229
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6907,7 +6843,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -6919,19 +6855,18 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -6947,7 +6882,7 @@
 </t>
         </is>
       </c>
-      <c r="R44" s="8" t="inlineStr">
+      <c r="R44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
@@ -6955,19 +6890,19 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1123
+</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6977,30 +6912,24 @@
 </t>
         </is>
       </c>
-      <c r="W44" s="8" t="inlineStr">
+      <c r="W44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
         </is>
       </c>
-      <c r="X44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">508
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -7014,58 +6943,63 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18011
+</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15551
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4119
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11021
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">7211
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263
+          <t xml:space="preserve">523
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12919
+          <t xml:space="preserve">12818
 </t>
         </is>
       </c>
@@ -7077,73 +7011,68 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022615
+          <t xml:space="preserve">12265
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9204
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">1700
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0118
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1026
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="n"/>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">1442
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01010
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 8
+          <t xml:space="preserve">1 1
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12224
+          <t xml:space="preserve">12229
 </t>
         </is>
       </c>
@@ -7163,30 +7092,30 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">406
+</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -7198,7 +7127,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -7208,7 +7137,12 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -7229,7 +7163,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">494
 </t>
         </is>
       </c>
@@ -7247,7 +7181,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -7265,19 +7199,19 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -7289,13 +7223,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -767,7 +767,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -785,7 +785,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -803,13 +803,13 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
@@ -821,11 +821,11 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
+          <t xml:space="preserve">333
+</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">137
 </t>
@@ -833,7 +833,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -864,7 +864,8 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t xml:space="preserve">5127
+</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -873,19 +874,19 @@
 </t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">217
 </t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
@@ -911,7 +912,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
@@ -923,19 +924,14 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">1360
 </t>
         </is>
       </c>
@@ -951,9 +947,9 @@
 </t>
         </is>
       </c>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -965,37 +961,37 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">468
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
@@ -1020,7 +1016,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3068
+          <t xml:space="preserve">5048
 </t>
         </is>
       </c>
@@ -1044,7 +1040,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">0239
 </t>
         </is>
       </c>
@@ -1056,7 +1052,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1068,11 +1064,11 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
@@ -1084,21 +1080,16 @@
 </t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+      <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1400
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1108,7 +1099,7 @@
 </t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="R6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">152
 </t>
@@ -1116,7 +1107,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -1126,9 +1117,9 @@
 </t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -1140,7 +1131,8 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
@@ -1157,7 +1149,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
@@ -1182,11 +1174,10 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
-</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+          <t>353</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
@@ -1198,7 +1189,7 @@
 </t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -1206,7 +1197,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1224,7 +1215,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1236,13 +1227,13 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -1264,54 +1255,58 @@
 </t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>863</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">334
+</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1329,13 +1324,13 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2851
+          <t xml:space="preserve">4851
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -1359,35 +1354,35 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
@@ -1396,7 +1391,7 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32620
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
@@ -1426,41 +1421,45 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">143
 </t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">422
 </t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="n"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1476,22 +1475,28 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>196565</t>
+          <t xml:space="preserve">26361
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11697
+          <t xml:space="preserve">1697
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
+          <t xml:space="preserve">1233
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11134
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1506,25 +1511,25 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">1671
 </t>
         </is>
       </c>
@@ -1536,37 +1541,37 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">11830
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">487
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1650
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
@@ -1578,7 +1583,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12241
+          <t xml:space="preserve">2248
 </t>
         </is>
       </c>
@@ -1596,13 +1601,13 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11862
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -1637,27 +1642,28 @@
 </t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">232
 </t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">478
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1694,7 +1700,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1734,27 +1740,27 @@
 </t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11062
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1779,7 +1785,8 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1790,7 +1797,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
@@ -1806,21 +1813,21 @@
 </t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">469
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1844,7 +1851,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -1862,7 +1869,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1874,18 +1881,27 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="X11" s="3" t="n"/>
       <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
@@ -1910,17 +1926,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0217
-</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
@@ -1946,7 +1962,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1964,7 +1980,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -1976,25 +1992,24 @@
       </c>
       <c r="P12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -2004,7 +2019,7 @@
 </t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">292
 </t>
@@ -2012,31 +2027,31 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">623
+          <t xml:space="preserve">023
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14170
+          <t xml:space="preserve">470
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -2067,8 +2082,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2083,10 +2097,16 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="3" t="n"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2116,7 +2136,7 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -2134,7 +2154,7 @@
       </c>
       <c r="R13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -2150,9 +2170,9 @@
 </t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">440
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -2176,12 +2196,14 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2199,7 +2221,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
+          <t xml:space="preserve">4880
 </t>
         </is>
       </c>
@@ -2211,7 +2233,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2247,7 +2269,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2257,21 +2279,16 @@
 </t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
@@ -2281,21 +2298,21 @@
 </t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">303
 </t>
         </is>
       </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">045
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -2305,9 +2322,9 @@
 </t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">360
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2360
 </t>
         </is>
       </c>
@@ -2325,19 +2342,19 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -2356,23 +2373,26 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26521
+          <t xml:space="preserve">5529
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>731</t>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2411,21 +2431,16 @@
 </t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">104
 </t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+      <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">4180
 </t>
         </is>
       </c>
@@ -2435,49 +2450,66 @@
 </t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">310
 </t>
         </is>
       </c>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">008
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">380
+</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>981</t>
-        </is>
-      </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="n"/>
-      <c r="Z15" s="3" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -2493,25 +2525,25 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2572
+          <t xml:space="preserve">2377
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82916
+          <t xml:space="preserve">129 16
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">768
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11182
+          <t xml:space="preserve">21182
 </t>
         </is>
       </c>
@@ -2523,19 +2555,19 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">3973
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">562
+          <t xml:space="preserve">1362
 </t>
         </is>
       </c>
@@ -2545,22 +2577,27 @@
 </t>
         </is>
       </c>
-      <c r="L16" s="3" t="n"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8809
+</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22125
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
@@ -2572,13 +2609,13 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">1547
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">1736
 </t>
         </is>
       </c>
@@ -2590,13 +2627,13 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
@@ -2608,7 +2645,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2620,13 +2657,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458
+          <t xml:space="preserve">11458
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10244
+          <t xml:space="preserve">12244
 </t>
         </is>
       </c>
@@ -2645,19 +2682,20 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23134
+          <t xml:space="preserve">3154
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2666,7 +2704,7 @@
 </t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">185
 </t>
@@ -2680,7 +2718,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2692,7 +2730,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2710,13 +2748,13 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2746,22 +2784,23 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>9465</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">145
 </t>
@@ -2781,7 +2820,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2800,71 +2839,74 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321
-</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t xml:space="preserve">2521
+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">529
+</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1375
 </t>
         </is>
       </c>
@@ -2876,7 +2918,7 @@
       </c>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -2894,17 +2936,17 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">281
 </t>
@@ -2912,13 +2954,13 @@
       </c>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2930,7 +2972,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2949,7 +2991,8 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t xml:space="preserve">3264
+</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2982,10 +3025,15 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -2997,7 +3045,8 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>635</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -3014,7 +3063,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
@@ -3030,7 +3079,7 @@
 </t>
         </is>
       </c>
-      <c r="R19" s="8" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
@@ -3054,9 +3103,10 @@
 </t>
         </is>
       </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>969</t>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3067,19 +3117,19 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -3098,23 +3148,24 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3137,12 +3188,13 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">84
+</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -3158,9 +3210,9 @@
 </t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -3196,7 +3248,8 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>448</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -3207,11 +3260,11 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="inlineStr">
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
@@ -3225,7 +3278,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -3262,13 +3315,13 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">864
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -3280,7 +3333,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3298,17 +3351,17 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">757
-</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">115
 </t>
@@ -3322,7 +3375,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -3352,7 +3405,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -3362,15 +3415,15 @@
 </t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">863
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3388,8 +3441,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3407,7 +3459,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9363
+          <t xml:space="preserve">5363
 </t>
         </is>
       </c>
@@ -3447,7 +3499,7 @@
 </t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -3455,7 +3507,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
@@ -3465,7 +3517,7 @@
 </t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">107
 </t>
@@ -3473,16 +3525,11 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="n"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">92
@@ -3509,7 +3556,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -3519,7 +3566,7 @@
 </t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
+      <c r="V22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
@@ -3527,14 +3574,13 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3576,13 +3622,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11171
+          <t xml:space="preserve">1171
 </t>
         </is>
       </c>
@@ -3618,7 +3664,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
@@ -3630,37 +3676,32 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12720
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2544
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1544
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3686
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
@@ -3678,19 +3719,19 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1386
+          <t xml:space="preserve">1305
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
@@ -3702,7 +3743,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
@@ -3721,7 +3762,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t xml:space="preserve">5095
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3732,62 +3774,67 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">022
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2946
 </t>
         </is>
       </c>
@@ -3799,7 +3846,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -3835,7 +3882,8 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
@@ -3871,7 +3919,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">455
 </t>
         </is>
       </c>
@@ -3883,131 +3931,133 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400
+</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">177
 </t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0248
-</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010
-</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="S25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">373
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
+      <c r="W25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
         </is>
       </c>
-      <c r="X25" s="3" t="inlineStr">
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">92
 </t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11121
+          <t xml:space="preserve">4573
 </t>
         </is>
       </c>
@@ -4036,7 +4086,7 @@
 </t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
@@ -4044,17 +4094,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -4078,13 +4128,13 @@
 </t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">105
 </t>
@@ -4110,7 +4160,8 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>993</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
@@ -4131,7 +4182,7 @@
 </t>
         </is>
       </c>
-      <c r="U26" s="3" t="inlineStr">
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">334
 </t>
@@ -4139,7 +4190,7 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -4151,19 +4202,20 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0220
+          <t xml:space="preserve">2220
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4181,13 +4233,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">501
+          <t xml:space="preserve">5501
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318 4
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -4217,11 +4269,11 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">104
 </t>
@@ -4247,19 +4299,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4269,7 +4321,7 @@
 </t>
         </is>
       </c>
-      <c r="R27" s="3" t="inlineStr">
+      <c r="R27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">145
 </t>
@@ -4277,47 +4329,49 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">1266
+</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4336,7 +4390,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16210
+          <t xml:space="preserve">6210
 </t>
         </is>
       </c>
@@ -4348,23 +4402,23 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
-</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">104
 </t>
@@ -4378,13 +4432,13 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4402,13 +4456,13 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -4420,7 +4474,8 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t xml:space="preserve">321
+</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
@@ -4431,23 +4486,23 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">5984
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">434
-</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
+          <t xml:space="preserve">934
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">277
 </t>
@@ -4461,7 +4516,7 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -4471,7 +4526,11 @@
 </t>
         </is>
       </c>
-      <c r="Z28" s="3" t="n"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -4487,7 +4546,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6248
+          <t xml:space="preserve">6249
 </t>
         </is>
       </c>
@@ -4503,9 +4562,9 @@
 </t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">383
 </t>
         </is>
       </c>
@@ -4529,12 +4588,13 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4570,7 +4630,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4592,7 +4652,7 @@
 </t>
         </is>
       </c>
-      <c r="U29" s="3" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">471
 </t>
@@ -4606,8 +4666,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
@@ -4624,7 +4683,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230090
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -4643,19 +4702,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22819
+          <t xml:space="preserve">27819
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15616
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
+          <t xml:space="preserve">745
 </t>
         </is>
       </c>
@@ -4673,25 +4732,25 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">570
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">2370
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -4715,7 +4774,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
@@ -4727,24 +4786,25 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4762,25 +4822,20 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="n"/>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1229
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4798,7 +4853,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">3364
 </t>
         </is>
       </c>
@@ -4838,27 +4893,22 @@
 </t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110 1
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -4874,7 +4924,7 @@
 </t>
         </is>
       </c>
-      <c r="P31" s="3" t="inlineStr">
+      <c r="P31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
@@ -4894,7 +4944,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4930,13 +4980,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4955,12 +5005,14 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">2086
+</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t xml:space="preserve">338
+</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4981,12 +5033,7 @@
 </t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">92
@@ -5001,13 +5048,13 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -5019,7 +5066,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5031,7 +5078,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -5055,43 +5102,36 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">11411
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
-</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="n"/>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -5110,7 +5150,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">4437
 </t>
         </is>
       </c>
@@ -5120,7 +5160,7 @@
 </t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">143
 </t>
@@ -5132,7 +5172,7 @@
 </t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">167
 </t>
@@ -5146,7 +5186,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5162,13 +5202,13 @@
 </t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">187
 </t>
         </is>
       </c>
-      <c r="M33" s="8" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
@@ -5176,7 +5216,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -5198,7 +5238,7 @@
 </t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr">
+      <c r="R33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">147
 </t>
@@ -5218,7 +5258,7 @@
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
@@ -5230,7 +5270,7 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5242,13 +5282,14 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
+          <t xml:space="preserve">14209
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">1139
+</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5276,10 +5317,9 @@
 </t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">056
-</t>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5288,7 +5328,7 @@
 </t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">152
 </t>
@@ -5296,13 +5336,13 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5324,15 +5364,15 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">814
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5356,19 +5396,19 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -5380,31 +5420,31 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="X34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180 16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5423,13 +5463,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4399
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -5445,13 +5485,13 @@
 </t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">133
 </t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">149
 </t>
@@ -5465,14 +5505,13 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -5489,7 +5528,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5505,16 +5544,21 @@
 </t>
         </is>
       </c>
-      <c r="Q35" s="3" t="n"/>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">589
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -5526,7 +5570,7 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
@@ -5550,11 +5594,16 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21215
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5576,24 +5625,28 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n"/>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">048
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
@@ -5601,10 +5654,16 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
@@ -5626,7 +5685,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
@@ -5650,19 +5709,19 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -5672,27 +5731,27 @@
 </t>
         </is>
       </c>
-      <c r="W36" s="8" t="inlineStr">
+      <c r="W36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">136
 </t>
         </is>
       </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
+      <c r="X36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11860
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5717,7 +5776,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118106
+          <t xml:space="preserve">1316
 </t>
         </is>
       </c>
@@ -5729,7 +5788,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -5741,7 +5800,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
@@ -5753,13 +5812,13 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
@@ -5771,31 +5830,31 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">032
+          <t xml:space="preserve">1532
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">447
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12402
+          <t xml:space="preserve">24092
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">3595
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133 5
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5813,7 +5872,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">1716
 </t>
         </is>
       </c>
@@ -5825,31 +5884,26 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">11411
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">498
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11812
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -5868,17 +5922,17 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4422
-</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
+          <t xml:space="preserve">4433
+</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
@@ -5890,15 +5944,15 @@
 </t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5910,17 +5964,12 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -5934,23 +5983,23 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="8" t="inlineStr">
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">267
 </t>
@@ -5958,13 +6007,13 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -5974,13 +6023,13 @@
 </t>
         </is>
       </c>
-      <c r="U38" s="3" t="inlineStr">
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">269
 </t>
         </is>
       </c>
-      <c r="V38" s="3" t="inlineStr">
+      <c r="V38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
@@ -6025,30 +6074,31 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9146
+          <t xml:space="preserve">59146
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">416
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
-</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08110
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -6060,29 +6110,29 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
+          <t xml:space="preserve">1580
+</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">102
 </t>
@@ -6090,7 +6140,8 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">9
+</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -6125,7 +6176,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -6147,7 +6198,7 @@
 </t>
         </is>
       </c>
-      <c r="X39" s="8" t="inlineStr">
+      <c r="X39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">114
 </t>
@@ -6161,7 +6212,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6180,12 +6231,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t xml:space="preserve">6171
+</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">907
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -6215,7 +6267,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6227,11 +6279,11 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
@@ -6245,13 +6297,13 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -6267,7 +6319,7 @@
 </t>
         </is>
       </c>
-      <c r="R40" s="8" t="inlineStr">
+      <c r="R40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
@@ -6275,7 +6327,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -6287,13 +6339,13 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">942
+</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680
 </t>
         </is>
       </c>
@@ -6303,7 +6355,7 @@
 </t>
         </is>
       </c>
-      <c r="X40" s="3" t="inlineStr">
+      <c r="X40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">101
 </t>
@@ -6311,13 +6363,14 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">3180
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">2236
+</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6347,25 +6400,24 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
+          <t>163</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">152
 </t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
@@ -6393,21 +6445,21 @@
 </t>
         </is>
       </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -6437,11 +6489,11 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">326
 </t>
@@ -6455,20 +6507,26 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="X41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">016
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="3" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
+      </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6492,7 +6550,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">392
 </t>
         </is>
       </c>
@@ -6502,7 +6560,7 @@
 </t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">233
 </t>
@@ -6510,7 +6568,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -6528,7 +6586,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -6544,7 +6602,7 @@
 </t>
         </is>
       </c>
-      <c r="M42" s="8" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">109
 </t>
@@ -6552,20 +6610,19 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -6588,7 +6645,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
@@ -6600,13 +6657,13 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -6618,11 +6675,16 @@
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+          <t xml:space="preserve">13920
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6638,13 +6700,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340
+          <t xml:space="preserve">2340
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -6662,13 +6724,13 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">041
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -6686,7 +6748,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6704,7 +6766,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -6716,7 +6778,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6740,11 +6802,11 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">314
 </t>
@@ -6758,7 +6820,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6776,7 +6838,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6795,7 +6857,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280
+          <t xml:space="preserve">2580
 </t>
         </is>
       </c>
@@ -6811,7 +6873,7 @@
 </t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">229
 </t>
@@ -6843,7 +6905,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">092
 </t>
         </is>
       </c>
@@ -6855,22 +6917,23 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
+          <t xml:space="preserve">6440
+</t>
+        </is>
+      </c>
+      <c r="P44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
@@ -6882,7 +6945,7 @@
 </t>
         </is>
       </c>
-      <c r="R44" s="3" t="inlineStr">
+      <c r="R44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
@@ -6896,13 +6959,13 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="U44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -6918,18 +6981,24 @@
 </t>
         </is>
       </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="X44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2279
+</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+          <t xml:space="preserve">2908
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6945,43 +7014,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18011
+          <t xml:space="preserve">23122
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11221
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">9108
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">71949
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7211
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -6993,89 +7061,84 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12818
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">12029
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12265
+          <t xml:space="preserve">2265
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">29084
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1700
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0815
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1780
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n"/>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="n"/>
+          <t xml:space="preserve">1369
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1826
+</t>
+        </is>
+      </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">2862
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1647
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="n"/>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -7092,16 +7155,17 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>5618</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">406
-</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
+          <t xml:space="preserve">5518
+</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">706
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">153
 </t>
@@ -7109,13 +7173,13 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -7127,7 +7191,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -7137,12 +7201,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -7151,19 +7210,19 @@
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
@@ -7181,13 +7240,13 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="S46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -7197,15 +7256,15 @@
 </t>
         </is>
       </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3908
+</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -7215,7 +7274,7 @@
 </t>
         </is>
       </c>
-      <c r="X46" s="3" t="inlineStr">
+      <c r="X46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -7223,13 +7282,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -737,110 +728,92 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
-</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
-</t>
+          <t>355</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
-        </is>
-      </c>
-      <c r="R4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>137</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U4" s="3" t="n"/>
@@ -864,141 +837,118 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>218</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">468
-</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>468</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1016,141 +966,118 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5048
-</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0239
-</t>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>231</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>152</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1168,8 +1095,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
-</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1179,134 +1105,112 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>243</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
-</t>
-        </is>
-      </c>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1324,135 +1228,113 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
-</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>116</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>362</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>133</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
-</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -1475,146 +1357,122 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26361
-</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
-</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11134
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
-</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
-</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
-</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248
-</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1632,136 +1490,114 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312
-</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>107</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
-</t>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>78</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>139</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
-</t>
+          <t>389</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11062
-</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1779,104 +1615,87 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">469
-</t>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1884,22 +1703,19 @@
           <t>42</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>310</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
         </is>
       </c>
       <c r="X11" s="3" t="n"/>
@@ -1920,8 +1736,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067
-</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1930,76 +1745,64 @@
         </is>
       </c>
       <c r="E12" s="3" t="n"/>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>199</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -2009,50 +1812,42 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>392</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">023
-</t>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2070,14 +1865,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
-</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -2087,123 +1880,103 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
-        </is>
-      </c>
-      <c r="R13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>153</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>440</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2221,141 +1994,118 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880
-</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>120</t>
         </is>
       </c>
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2360
-</t>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>360</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2373,141 +2123,118 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5529
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>163</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
         </is>
       </c>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>380</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2525,146 +2252,122 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2377
-</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129 16
-</t>
+          <t>159 6</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21182
-</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3973
-</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1362
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8809
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
-</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
-</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1736
-</t>
+          <t>736</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
-</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>725</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
-</t>
+          <t>483</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11458
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12244
-</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2682,146 +2385,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
-</t>
+          <t>376</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2839,141 +2518,118 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>321</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2991,146 +2647,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>126</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
-</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>269</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3158,134 +2790,112 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3303,140 +2913,117 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0422
-</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3459,123 +3046,103 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
-</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>107</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O22" s="3" t="n"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">390
-</t>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>390</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
@@ -3585,14 +3152,12 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3610,141 +3175,118 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25175
-</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
-</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
-</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
-</t>
+          <t>791</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
-</t>
+          <t>503</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
-</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
-</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305
-</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3762,146 +3304,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5095
-</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2946
-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3919,146 +3437,122 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>118</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
-</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="S25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>148</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>202</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>328</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4573
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4076,146 +3570,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
-</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>148</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">334
-</t>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>334</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4233,146 +3703,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
-</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>235</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="R27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4390,140 +3836,117 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
-</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>146</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5984
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
-</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4546,122 +3969,102 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">383
-</t>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>233</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">471
-</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>471</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
@@ -4671,20 +4074,17 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4702,128 +4102,107 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
-</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
-</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2370
-</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
-</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
-</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="X30" s="3" t="n"/>
@@ -4834,8 +4213,7 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4853,141 +4231,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3364
-</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">465
-</t>
-        </is>
-      </c>
-      <c r="P31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>103</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5005,105 +4360,88 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
-</t>
+          <t>338</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>120</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
-</t>
+          <t>336</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5113,14 +4451,12 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="X32" s="3" t="n"/>
@@ -5131,8 +4467,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5150,146 +4485,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>167</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>147</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">834
-</t>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>234</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="X33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>111</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5307,14 +4618,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -5324,128 +4633,107 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>152</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>522</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="X34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5463,50 +4751,42 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
-</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -5516,92 +4796,77 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="R35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">589
-</t>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>159</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5619,8 +4884,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5630,129 +4894,108 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">048
-</t>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>143</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="X36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">806
-</t>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>106</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5770,141 +5013,118 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22166
-</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1316
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>827</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">447
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24092
-</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
-</t>
+          <t>593</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>479</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1340
-</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
-</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>070</t>
         </is>
       </c>
       <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5922,141 +5142,118 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
-</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>228</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6074,146 +5271,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59146
-</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>217</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1580
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>102</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>294</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6231,146 +5404,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2680
-</t>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>260</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="X40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6388,14 +5537,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5875
-</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6403,130 +5550,109 @@
           <t>163</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">530
-</t>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
-      <c r="P41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>108</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
-</t>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>326</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6544,80 +5670,67 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
-</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">392
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -6627,62 +5740,52 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13920
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6700,146 +5803,122 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340
-</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>314</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6857,146 +5936,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
-</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>229</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">092
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440
-</t>
-        </is>
-      </c>
-      <c r="P44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>106</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="R44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>328</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="X44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2279
-</t>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>129</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2908
-</t>
+          <t>508</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -7014,14 +6069,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23122
-</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
-</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -7031,111 +6084,93 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9108
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71949
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
-</t>
+          <t>523</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12029
-</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
-</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29084
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780
-</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="R45" s="3" t="n"/>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1369
-</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2862
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647
-</t>
+          <t>547</t>
         </is>
       </c>
       <c r="Y45" s="3" t="n"/>
@@ -7155,141 +6190,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">706
-</t>
+          <t>5518</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>206</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>108</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="S46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">390
-</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3908
-</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="X46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>108</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>124</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>317</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -2179,7 +2179,7 @@
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>362</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>76</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>375</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>404</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O22" s="3" t="n"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>222</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>272</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>011</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>194</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>62</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>358</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>318</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>62</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>014</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>322</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>340</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>358</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>670</t>
         </is>
       </c>
       <c r="X37" s="3" t="n"/>
@@ -5180,7 +5180,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K38" s="3" t="n"/>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t>168</t>
@@ -5193,7 +5197,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -5223,7 +5227,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -5331,7 +5335,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5404,7 +5408,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5459,7 +5463,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5592,7 +5596,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5770,12 +5774,12 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -5843,7 +5847,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -5903,7 +5907,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -5976,7 +5980,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -5991,12 +5995,12 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>440</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -6021,7 +6025,7 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>193</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
@@ -6069,7 +6073,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6084,7 +6088,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -6104,7 +6108,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>323</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6119,12 +6123,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>270</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6165,12 +6169,12 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="Y45" s="3" t="n"/>
@@ -6195,7 +6199,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6210,7 +6214,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>153</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -6245,7 +6249,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6290,7 +6294,7 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
@@ -6300,7 +6304,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>311</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_digit_manipulation.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>517</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2050,7 +2050,7 @@
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -2179,7 +2179,7 @@
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>725</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>554</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>175</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O22" s="3" t="n"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>690</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>099</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>520</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>94</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>558</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>004</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>108</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>332</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>341</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>070</t>
         </is>
       </c>
       <c r="X37" s="3" t="n"/>
@@ -5180,11 +5180,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t>168</t>
@@ -5197,7 +5193,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>97</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -5295,7 +5291,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -5330,7 +5326,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5463,7 +5459,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5493,7 +5489,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>195</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
@@ -5596,7 +5592,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5646,7 +5642,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5774,12 +5770,12 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>118</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -5862,7 +5858,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5940,7 +5936,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -5995,7 +5991,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -6025,7 +6021,7 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>198</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
@@ -6045,7 +6041,7 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>109</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -6073,7 +6069,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6098,7 +6094,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>719</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6108,7 +6104,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>523</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6123,12 +6119,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>650</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>578</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6159,7 +6155,7 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>647</t>
         </is>
       </c>
       <c r="Y45" s="3" t="n"/>
@@ -6234,7 +6230,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6249,7 +6245,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6294,7 +6290,7 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
@@ -6304,7 +6300,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
